--- a/output/roomself_excel/12716.xlsx
+++ b/output/roomself_excel/12716.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>41895</v>
+        <v>227010</v>
       </c>
       <c r="D2" t="n">
-        <v>1728</v>
+        <v>3848</v>
       </c>
       <c r="E2" t="n">
-        <v>313</v>
+        <v>510</v>
       </c>
       <c r="F2" t="n">
-        <v>175</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>57304</v>
+        <v>747734</v>
       </c>
       <c r="D3" t="n">
-        <v>1916</v>
+        <v>10760</v>
       </c>
       <c r="E3" t="n">
-        <v>556</v>
+        <v>898</v>
       </c>
       <c r="F3" t="n">
-        <v>187</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17908</v>
+        <v>149940</v>
       </c>
       <c r="D4" t="n">
-        <v>1076</v>
+        <v>3124</v>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>469</v>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
+        <v>368</v>
       </c>
     </row>
     <row r="5">
@@ -532,17 +532,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>39144</v>
+        <v>198905</v>
       </c>
       <c r="D5" t="n">
-        <v>1604</v>
+        <v>4172</v>
       </c>
       <c r="E5" t="n">
-        <v>168</v>
+        <v>566</v>
       </c>
       <c r="F5" t="n">
         <v>28</v>
@@ -554,17 +554,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>46833</v>
+        <v>17908</v>
       </c>
       <c r="D6" t="n">
-        <v>1736</v>
+        <v>1076</v>
       </c>
       <c r="E6" t="n">
-        <v>201</v>
+        <v>148</v>
       </c>
       <c r="F6" t="n">
         <v>28</v>
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1317881</v>
+        <v>38097</v>
       </c>
       <c r="D7" t="n">
-        <v>20148</v>
+        <v>1608</v>
       </c>
       <c r="E7" t="n">
-        <v>1627</v>
+        <v>153</v>
       </c>
       <c r="F7" t="n">
-        <v>1498</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
@@ -602,16 +602,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38097</v>
+        <v>141180</v>
       </c>
       <c r="D8" t="n">
-        <v>1608</v>
+        <v>4768</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -620,20 +620,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>39342</v>
+        <v>43948</v>
       </c>
       <c r="D9" t="n">
-        <v>1628</v>
+        <v>1728</v>
       </c>
       <c r="E9" t="n">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="F9" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10">
@@ -642,20 +642,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>149940</v>
+        <v>18207</v>
       </c>
       <c r="D10" t="n">
-        <v>3124</v>
+        <v>1088</v>
       </c>
       <c r="E10" t="n">
-        <v>469</v>
+        <v>186</v>
       </c>
       <c r="F10" t="n">
-        <v>368</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>95879</v>
+        <v>512320</v>
       </c>
       <c r="D11" t="n">
-        <v>2800</v>
+        <v>13143</v>
       </c>
       <c r="E11" t="n">
-        <v>1015</v>
+        <v>1151</v>
       </c>
       <c r="F11" t="n">
-        <v>332</v>
+        <v>705</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>141180</v>
+        <v>65079</v>
       </c>
       <c r="D12" t="n">
-        <v>4768</v>
+        <v>2588</v>
       </c>
       <c r="E12" t="n">
-        <v>1017</v>
+        <v>234</v>
       </c>
       <c r="F12" t="n">
-        <v>719</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13">
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>54720</v>
+        <v>39144</v>
       </c>
       <c r="D13" t="n">
-        <v>1908</v>
+        <v>1604</v>
       </c>
       <c r="E13" t="n">
-        <v>192</v>
+        <v>168</v>
       </c>
       <c r="F13" t="n">
         <v>28</v>
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>54332</v>
+        <v>39342</v>
       </c>
       <c r="D14" t="n">
-        <v>3468</v>
+        <v>1628</v>
       </c>
       <c r="E14" t="n">
-        <v>1092</v>
+        <v>158</v>
       </c>
       <c r="F14" t="n">
-        <v>705</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -756,16 +756,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>73914</v>
+        <v>54720</v>
       </c>
       <c r="D15" t="n">
-        <v>2300</v>
+        <v>1908</v>
       </c>
       <c r="E15" t="n">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="F15" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -774,20 +774,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>512320</v>
+        <v>73914</v>
       </c>
       <c r="D16" t="n">
-        <v>13143</v>
+        <v>2300</v>
       </c>
       <c r="E16" t="n">
-        <v>1612</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>970</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -818,20 +818,20 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>204930</v>
+        <v>58422</v>
       </c>
       <c r="D18" t="n">
-        <v>3636</v>
+        <v>2012</v>
       </c>
       <c r="E18" t="n">
-        <v>1026</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>495</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -840,20 +840,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>43948</v>
+        <v>170715</v>
       </c>
       <c r="D19" t="n">
-        <v>1728</v>
+        <v>3536</v>
       </c>
       <c r="E19" t="n">
-        <v>151</v>
+        <v>626</v>
       </c>
       <c r="F19" t="n">
-        <v>12</v>
+        <v>313</v>
       </c>
     </row>
     <row r="20">
@@ -862,20 +862,20 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58422</v>
+        <v>41895</v>
       </c>
       <c r="D20" t="n">
-        <v>2012</v>
+        <v>1728</v>
       </c>
       <c r="E20" t="n">
-        <v>287</v>
+        <v>313</v>
       </c>
       <c r="F20" t="n">
-        <v>10</v>
+        <v>175</v>
       </c>
     </row>
     <row r="21">
@@ -884,20 +884,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>170715</v>
+        <v>57304</v>
       </c>
       <c r="D21" t="n">
-        <v>3536</v>
+        <v>1916</v>
       </c>
       <c r="E21" t="n">
-        <v>626</v>
+        <v>232</v>
       </c>
       <c r="F21" t="n">
-        <v>313</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22">
@@ -910,16 +910,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>36157</v>
+        <v>46833</v>
       </c>
       <c r="D22" t="n">
-        <v>1528</v>
+        <v>1736</v>
       </c>
       <c r="E22" t="n">
-        <v>441</v>
+        <v>201</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23">
@@ -932,16 +932,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>137114</v>
+        <v>95879</v>
       </c>
       <c r="D23" t="n">
-        <v>2964</v>
+        <v>2800</v>
       </c>
       <c r="E23" t="n">
-        <v>412</v>
+        <v>428</v>
       </c>
       <c r="F23" t="n">
-        <v>109</v>
+        <v>332</v>
       </c>
     </row>
     <row r="24">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>210124</v>
+        <v>54332</v>
       </c>
       <c r="D24" t="n">
-        <v>4182</v>
+        <v>3468</v>
       </c>
       <c r="E24" t="n">
-        <v>863</v>
+        <v>833</v>
       </c>
       <c r="F24" t="n">
-        <v>831</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -976,16 +976,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>37260</v>
+        <v>204930</v>
       </c>
       <c r="D25" t="n">
-        <v>2016</v>
+        <v>3636</v>
       </c>
       <c r="E25" t="n">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="F25" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26">
@@ -998,16 +998,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>24566</v>
+        <v>144232</v>
       </c>
       <c r="D26" t="n">
-        <v>1260</v>
+        <v>3716</v>
       </c>
       <c r="E26" t="n">
-        <v>185</v>
+        <v>294</v>
       </c>
       <c r="F26" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27">
@@ -1016,20 +1016,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18207</v>
+        <v>36157</v>
       </c>
       <c r="D27" t="n">
-        <v>1088</v>
+        <v>1528</v>
       </c>
       <c r="E27" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1038,20 +1038,86 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>65079</v>
+        <v>137114</v>
       </c>
       <c r="D28" t="n">
-        <v>2588</v>
+        <v>2964</v>
       </c>
       <c r="E28" t="n">
-        <v>541</v>
+        <v>412</v>
       </c>
       <c r="F28" t="n">
-        <v>435</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>210124</v>
+      </c>
+      <c r="D29" t="n">
+        <v>4182</v>
+      </c>
+      <c r="E29" t="n">
+        <v>665</v>
+      </c>
+      <c r="F29" t="n">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>37260</v>
+      </c>
+      <c r="D30" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E30" t="n">
+        <v>448</v>
+      </c>
+      <c r="F30" t="n">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>24566</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1260</v>
+      </c>
+      <c r="E31" t="n">
+        <v>185</v>
+      </c>
+      <c r="F31" t="n">
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/12716.xlsx
+++ b/output/roomself_excel/12716.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:V31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,92 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_6</t>
         </is>
       </c>
     </row>
@@ -475,12 +555,32 @@
       <c r="D2" t="n">
         <v>3848</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>510</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>28</v>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +597,48 @@
       <c r="D3" t="n">
         <v>10760</v>
       </c>
-      <c r="E3" t="n">
-        <v>898</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>439</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="G3" t="n">
+        <v>28</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>358</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>843</v>
+      </c>
+      <c r="M3" t="n">
+        <v>27</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +655,40 @@
       <c r="D4" t="n">
         <v>3124</v>
       </c>
-      <c r="E4" t="n">
-        <v>469</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>368</v>
-      </c>
+        <v>340</v>
+      </c>
+      <c r="G4" t="n">
+        <v>28</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>441</v>
+      </c>
+      <c r="J4" t="n">
+        <v>28</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +705,32 @@
       <c r="D5" t="n">
         <v>4172</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>566</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>28</v>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +747,32 @@
       <c r="D6" t="n">
         <v>1076</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>148</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>28</v>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +789,32 @@
       <c r="D7" t="n">
         <v>1608</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>153</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>28</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +831,24 @@
       <c r="D8" t="n">
         <v>4768</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0</v>
-      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +865,32 @@
       <c r="D9" t="n">
         <v>1728</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
         <v>151</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>12</v>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +907,40 @@
       <c r="D10" t="n">
         <v>1088</v>
       </c>
-      <c r="E10" t="n">
-        <v>186</v>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F10" t="n">
-        <v>60</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>33</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>153</v>
+      </c>
+      <c r="J10" t="n">
+        <v>11</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +957,40 @@
       <c r="D11" t="n">
         <v>13143</v>
       </c>
-      <c r="E11" t="n">
-        <v>1151</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>705</v>
-      </c>
+        <v>280</v>
+      </c>
+      <c r="G11" t="n">
+        <v>12</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>737</v>
+      </c>
+      <c r="J11" t="n">
+        <v>15</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +1007,56 @@
       <c r="D12" t="n">
         <v>2588</v>
       </c>
-      <c r="E12" t="n">
-        <v>234</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>173</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="G12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M12" t="n">
+        <v>11</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="O12" t="n">
+        <v>177</v>
+      </c>
+      <c r="P12" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +1073,32 @@
       <c r="D13" t="n">
         <v>1604</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>168</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>28</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +1115,32 @@
       <c r="D14" t="n">
         <v>1628</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
         <v>158</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>28</v>
       </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +1157,32 @@
       <c r="D15" t="n">
         <v>1908</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
         <v>192</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>28</v>
       </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1199,24 @@
       <c r="D16" t="n">
         <v>2300</v>
       </c>
-      <c r="E16" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1233,48 @@
       <c r="D17" t="n">
         <v>2464</v>
       </c>
-      <c r="E17" t="n">
-        <v>438</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>211</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="G17" t="n">
+        <v>11</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>34</v>
+      </c>
+      <c r="J17" t="n">
+        <v>12</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L17" t="n">
+        <v>427</v>
+      </c>
+      <c r="M17" t="n">
+        <v>10</v>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,12 +1291,24 @@
       <c r="D18" t="n">
         <v>2012</v>
       </c>
-      <c r="E18" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -849,12 +1325,40 @@
       <c r="D19" t="n">
         <v>3536</v>
       </c>
-      <c r="E19" t="n">
-        <v>626</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
-        <v>313</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="G19" t="n">
+        <v>28</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>285</v>
+      </c>
+      <c r="J19" t="n">
+        <v>27</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -871,12 +1375,40 @@
       <c r="D20" t="n">
         <v>1728</v>
       </c>
-      <c r="E20" t="n">
-        <v>313</v>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F20" t="n">
-        <v>175</v>
-      </c>
+        <v>285</v>
+      </c>
+      <c r="G20" t="n">
+        <v>28</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>147</v>
+      </c>
+      <c r="J20" t="n">
+        <v>28</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -893,12 +1425,32 @@
       <c r="D21" t="n">
         <v>1916</v>
       </c>
-      <c r="E21" t="n">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
         <v>232</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>28</v>
       </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -915,12 +1467,32 @@
       <c r="D22" t="n">
         <v>1736</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
         <v>201</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>28</v>
       </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -937,11 +1509,71 @@
       <c r="D23" t="n">
         <v>2800</v>
       </c>
-      <c r="E23" t="n">
-        <v>428</v>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>332</v>
+        <v>355</v>
+      </c>
+      <c r="G23" t="n">
+        <v>28</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>42</v>
+      </c>
+      <c r="J23" t="n">
+        <v>37</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>40</v>
+      </c>
+      <c r="M23" t="n">
+        <v>32</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>110</v>
+      </c>
+      <c r="P23" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="R23" t="n">
+        <v>191</v>
+      </c>
+      <c r="S23" t="n">
+        <v>12</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="U23" t="n">
+        <v>47</v>
+      </c>
+      <c r="V23" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="24">
@@ -959,12 +1591,40 @@
       <c r="D24" t="n">
         <v>3468</v>
       </c>
-      <c r="E24" t="n">
-        <v>833</v>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>77</v>
-      </c>
+        <v>799</v>
+      </c>
+      <c r="G24" t="n">
+        <v>11</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>66</v>
+      </c>
+      <c r="J24" t="n">
+        <v>34</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr"/>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,12 +1641,32 @@
       <c r="D25" t="n">
         <v>3636</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
         <v>482</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>34</v>
       </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr"/>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1003,12 +1683,32 @@
       <c r="D26" t="n">
         <v>3716</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
         <v>294</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>34</v>
       </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr"/>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1025,12 +1725,24 @@
       <c r="D27" t="n">
         <v>1528</v>
       </c>
-      <c r="E27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1047,12 +1759,40 @@
       <c r="D28" t="n">
         <v>2964</v>
       </c>
-      <c r="E28" t="n">
-        <v>412</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>109</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="G28" t="n">
+        <v>29</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>383</v>
+      </c>
+      <c r="J28" t="n">
+        <v>27</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1069,12 +1809,56 @@
       <c r="D29" t="n">
         <v>4182</v>
       </c>
-      <c r="E29" t="n">
-        <v>665</v>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F29" t="n">
-        <v>429</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="G29" t="n">
+        <v>38</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>354</v>
+      </c>
+      <c r="J29" t="n">
+        <v>26</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>798</v>
+      </c>
+      <c r="M29" t="n">
+        <v>12</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>79</v>
+      </c>
+      <c r="P29" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1091,12 +1875,40 @@
       <c r="D30" t="n">
         <v>2016</v>
       </c>
-      <c r="E30" t="n">
-        <v>448</v>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F30" t="n">
-        <v>105</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="G30" t="n">
+        <v>34</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>414</v>
+      </c>
+      <c r="J30" t="n">
+        <v>15</v>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr"/>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1113,12 +1925,40 @@
       <c r="D31" t="n">
         <v>1260</v>
       </c>
-      <c r="E31" t="n">
-        <v>185</v>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>80</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="G31" t="n">
+        <v>12</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>173</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12</v>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/roomself_excel/12716.xlsx
+++ b/output/roomself_excel/12716.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V31"/>
+  <dimension ref="A1:AT31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,6 +537,126 @@
       <c r="V1" s="1" t="inlineStr">
         <is>
           <t>ExtWallWidth_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_1</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_2</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_2</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_3</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_3</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_3</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_4</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_4</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_4</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_4</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_5</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_5</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_5</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_5</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>OpenType_6</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>OpenDir_6</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>OpenLength_6</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>OpenWidth_6</t>
         </is>
       </c>
     </row>
@@ -581,6 +701,42 @@
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>147</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -639,6 +795,54 @@
       <c r="T3" t="inlineStr"/>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>334</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>327</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -689,6 +893,42 @@
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>190</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -731,6 +971,42 @@
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>381</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -773,6 +1049,30 @@
       <c r="T6" t="inlineStr"/>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -815,6 +1115,42 @@
       <c r="T7" t="inlineStr"/>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>151</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -849,6 +1185,30 @@
       <c r="T8" t="inlineStr"/>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -891,6 +1251,30 @@
       <c r="T9" t="inlineStr"/>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -941,6 +1325,42 @@
       <c r="T10" t="inlineStr"/>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>48</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>33</v>
+      </c>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -991,6 +1411,42 @@
       <c r="T11" t="inlineStr"/>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>35</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1057,6 +1513,54 @@
       <c r="T12" t="inlineStr"/>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>58</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC12" t="n">
+        <v>109</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1099,6 +1603,30 @@
       <c r="T13" t="inlineStr"/>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1141,6 +1669,42 @@
       <c r="T14" t="inlineStr"/>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>149</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1183,6 +1747,42 @@
       <c r="T15" t="inlineStr"/>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>91</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1217,6 +1817,30 @@
       <c r="T16" t="inlineStr"/>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1275,6 +1899,30 @@
       <c r="T17" t="inlineStr"/>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1309,6 +1957,30 @@
       <c r="T18" t="inlineStr"/>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="inlineStr"/>
+      <c r="AH18" t="inlineStr"/>
+      <c r="AI18" t="inlineStr"/>
+      <c r="AJ18" t="inlineStr"/>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="inlineStr"/>
+      <c r="AO18" t="inlineStr"/>
+      <c r="AP18" t="inlineStr"/>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="inlineStr"/>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1359,6 +2031,54 @@
       <c r="T19" t="inlineStr"/>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>282</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC19" t="n">
+        <v>252</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE19" t="inlineStr"/>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="inlineStr"/>
+      <c r="AH19" t="inlineStr"/>
+      <c r="AI19" t="inlineStr"/>
+      <c r="AJ19" t="inlineStr"/>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="inlineStr"/>
+      <c r="AO19" t="inlineStr"/>
+      <c r="AP19" t="inlineStr"/>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="inlineStr"/>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1409,6 +2129,42 @@
       <c r="T20" t="inlineStr"/>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>90</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1451,6 +2207,42 @@
       <c r="T21" t="inlineStr"/>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>147</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1493,6 +2285,42 @@
       <c r="T22" t="inlineStr"/>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>151</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1574,6 +2402,102 @@
       </c>
       <c r="V23" t="n">
         <v>13</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y23" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AG23" t="n">
+        <v>14</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AK23" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>11</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AO23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1625,6 +2549,30 @@
       <c r="T24" t="inlineStr"/>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr"/>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+      <c r="AE24" t="inlineStr"/>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="inlineStr"/>
+      <c r="AH24" t="inlineStr"/>
+      <c r="AI24" t="inlineStr"/>
+      <c r="AJ24" t="inlineStr"/>
+      <c r="AK24" t="inlineStr"/>
+      <c r="AL24" t="inlineStr"/>
+      <c r="AM24" t="inlineStr"/>
+      <c r="AN24" t="inlineStr"/>
+      <c r="AO24" t="inlineStr"/>
+      <c r="AP24" t="inlineStr"/>
+      <c r="AQ24" t="inlineStr"/>
+      <c r="AR24" t="inlineStr"/>
+      <c r="AS24" t="inlineStr"/>
+      <c r="AT24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1667,6 +2615,54 @@
       <c r="T25" t="inlineStr"/>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y25" t="n">
+        <v>365</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC25" t="n">
+        <v>89</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE25" t="inlineStr"/>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="inlineStr"/>
+      <c r="AH25" t="inlineStr"/>
+      <c r="AI25" t="inlineStr"/>
+      <c r="AJ25" t="inlineStr"/>
+      <c r="AK25" t="inlineStr"/>
+      <c r="AL25" t="inlineStr"/>
+      <c r="AM25" t="inlineStr"/>
+      <c r="AN25" t="inlineStr"/>
+      <c r="AO25" t="inlineStr"/>
+      <c r="AP25" t="inlineStr"/>
+      <c r="AQ25" t="inlineStr"/>
+      <c r="AR25" t="inlineStr"/>
+      <c r="AS25" t="inlineStr"/>
+      <c r="AT25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1709,6 +2705,54 @@
       <c r="T26" t="inlineStr"/>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="Y26" t="n">
+        <v>196</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC26" t="n">
+        <v>88</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE26" t="inlineStr"/>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="inlineStr"/>
+      <c r="AH26" t="inlineStr"/>
+      <c r="AI26" t="inlineStr"/>
+      <c r="AJ26" t="inlineStr"/>
+      <c r="AK26" t="inlineStr"/>
+      <c r="AL26" t="inlineStr"/>
+      <c r="AM26" t="inlineStr"/>
+      <c r="AN26" t="inlineStr"/>
+      <c r="AO26" t="inlineStr"/>
+      <c r="AP26" t="inlineStr"/>
+      <c r="AQ26" t="inlineStr"/>
+      <c r="AR26" t="inlineStr"/>
+      <c r="AS26" t="inlineStr"/>
+      <c r="AT26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1743,6 +2787,30 @@
       <c r="T27" t="inlineStr"/>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+      <c r="AH27" t="inlineStr"/>
+      <c r="AI27" t="inlineStr"/>
+      <c r="AJ27" t="inlineStr"/>
+      <c r="AK27" t="inlineStr"/>
+      <c r="AL27" t="inlineStr"/>
+      <c r="AM27" t="inlineStr"/>
+      <c r="AN27" t="inlineStr"/>
+      <c r="AO27" t="inlineStr"/>
+      <c r="AP27" t="inlineStr"/>
+      <c r="AQ27" t="inlineStr"/>
+      <c r="AR27" t="inlineStr"/>
+      <c r="AS27" t="inlineStr"/>
+      <c r="AT27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1793,6 +2861,54 @@
       <c r="T28" t="inlineStr"/>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y28" t="n">
+        <v>81</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>29</v>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AC28" t="n">
+        <v>141</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>27</v>
+      </c>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+      <c r="AH28" t="inlineStr"/>
+      <c r="AI28" t="inlineStr"/>
+      <c r="AJ28" t="inlineStr"/>
+      <c r="AK28" t="inlineStr"/>
+      <c r="AL28" t="inlineStr"/>
+      <c r="AM28" t="inlineStr"/>
+      <c r="AN28" t="inlineStr"/>
+      <c r="AO28" t="inlineStr"/>
+      <c r="AP28" t="inlineStr"/>
+      <c r="AQ28" t="inlineStr"/>
+      <c r="AR28" t="inlineStr"/>
+      <c r="AS28" t="inlineStr"/>
+      <c r="AT28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1859,6 +2975,66 @@
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="Y29" t="n">
+        <v>350</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="AC29" t="n">
+        <v>65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>66</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI29" t="inlineStr"/>
+      <c r="AJ29" t="inlineStr"/>
+      <c r="AK29" t="inlineStr"/>
+      <c r="AL29" t="inlineStr"/>
+      <c r="AM29" t="inlineStr"/>
+      <c r="AN29" t="inlineStr"/>
+      <c r="AO29" t="inlineStr"/>
+      <c r="AP29" t="inlineStr"/>
+      <c r="AQ29" t="inlineStr"/>
+      <c r="AR29" t="inlineStr"/>
+      <c r="AS29" t="inlineStr"/>
+      <c r="AT29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1909,6 +3085,30 @@
       <c r="T30" t="inlineStr"/>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+      <c r="AH30" t="inlineStr"/>
+      <c r="AI30" t="inlineStr"/>
+      <c r="AJ30" t="inlineStr"/>
+      <c r="AK30" t="inlineStr"/>
+      <c r="AL30" t="inlineStr"/>
+      <c r="AM30" t="inlineStr"/>
+      <c r="AN30" t="inlineStr"/>
+      <c r="AO30" t="inlineStr"/>
+      <c r="AP30" t="inlineStr"/>
+      <c r="AQ30" t="inlineStr"/>
+      <c r="AR30" t="inlineStr"/>
+      <c r="AS30" t="inlineStr"/>
+      <c r="AT30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1959,6 +3159,30 @@
       <c r="T31" t="inlineStr"/>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr"/>
+      <c r="AH31" t="inlineStr"/>
+      <c r="AI31" t="inlineStr"/>
+      <c r="AJ31" t="inlineStr"/>
+      <c r="AK31" t="inlineStr"/>
+      <c r="AL31" t="inlineStr"/>
+      <c r="AM31" t="inlineStr"/>
+      <c r="AN31" t="inlineStr"/>
+      <c r="AO31" t="inlineStr"/>
+      <c r="AP31" t="inlineStr"/>
+      <c r="AQ31" t="inlineStr"/>
+      <c r="AR31" t="inlineStr"/>
+      <c r="AS31" t="inlineStr"/>
+      <c r="AT31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
